--- a/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
+++ b/InputData/indst/SoCaOMSbRIC/Share of Capital and OM Spending by ISIC Code.xlsx
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4781643011829615</v>
+        <v>0.45630816353267</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.4781643011829615</v>
+        <v>0.45630816353267</v>
       </c>
     </row>
     <row r="11">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.04258639396614965</v>
+        <v>0.04437004750051631</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.04258639396614965</v>
+        <v>0.04437004750051631</v>
       </c>
     </row>
     <row r="12">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1808024634415262</v>
+        <v>0.1883750452665103</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.1808024634415262</v>
+        <v>0.1883750452665103</v>
       </c>
     </row>
     <row r="13">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.2139060571318126</v>
+        <v>0.2228651226758185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.2139060571318126</v>
+        <v>0.2228651226758185</v>
       </c>
     </row>
     <row r="14">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.08454078427755009</v>
+        <v>0.08808162102448482</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.08454078427755009</v>
+        <v>0.08808162102448482</v>
       </c>
     </row>
     <row r="15">
